--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/process_capability_summary_pdf_export_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/process_capability_summary_pdf_export_testcases.xlsx
@@ -246,7 +246,7 @@
       </c>
       <c r="L2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M2" t="inlineStr" s="2">
@@ -273,17 +273,17 @@
     <row r="3" ht="64" customHeight="1">
       <c r="A3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">方案执行</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">工艺能力汇总</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出 PDF</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="2">
@@ -335,7 +335,7 @@
       </c>
       <c r="L3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M3" t="inlineStr" s="2">
@@ -362,17 +362,17 @@
     <row r="4" ht="64" customHeight="1">
       <c r="A4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">方案执行</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">工艺能力汇总</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出 PDF</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="2">
@@ -424,7 +424,7 @@
       </c>
       <c r="L4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M4" t="inlineStr" s="2">
@@ -451,17 +451,17 @@
     <row r="5" ht="64" customHeight="1">
       <c r="A5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">方案执行</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">工艺能力汇总</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出 PDF</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D5" t="inlineStr" s="2">
@@ -513,7 +513,7 @@
       </c>
       <c r="L5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M5" t="inlineStr" s="2">
@@ -540,17 +540,17 @@
     <row r="6" ht="64" customHeight="1">
       <c r="A6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">方案执行</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">工艺能力汇总</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出 PDF</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="2">
@@ -602,7 +602,7 @@
       </c>
       <c r="L6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M6" t="inlineStr" s="2">
@@ -629,17 +629,17 @@
     <row r="7" ht="64" customHeight="1">
       <c r="A7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">方案执行</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">工艺能力汇总</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出 PDF</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="2">
@@ -691,7 +691,7 @@
       </c>
       <c r="L7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M7" t="inlineStr" s="2">
@@ -718,17 +718,17 @@
     <row r="8" ht="64" customHeight="1">
       <c r="A8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">方案执行</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">工艺能力汇总</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出 PDF</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="2">
@@ -778,7 +778,7 @@
       </c>
       <c r="L8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M8" t="inlineStr" s="2">
@@ -805,17 +805,17 @@
     <row r="9" ht="64" customHeight="1">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">方案执行</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">工艺能力汇总</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出 PDF</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="2">
@@ -865,7 +865,7 @@
       </c>
       <c r="L9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M9" t="inlineStr" s="2">
@@ -892,17 +892,17 @@
     <row r="10" ht="64" customHeight="1">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">方案执行</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">工艺能力汇总</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出 PDF</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="2">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M10" t="inlineStr" s="2">
@@ -981,17 +981,17 @@
     <row r="11" ht="64" customHeight="1">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">方案执行</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">工艺能力汇总</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出 PDF</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="2">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="L11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M11" t="inlineStr" s="2">
@@ -1069,17 +1069,17 @@
     <row r="12" ht="64" customHeight="1">
       <c r="A12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">方案执行</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">工艺能力汇总</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出 PDF</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="2">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="L12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M12" t="inlineStr" s="2">
@@ -1157,17 +1157,17 @@
     <row r="13" ht="64" customHeight="1">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">方案执行</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">工艺能力汇总</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出 PDF</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="2">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="L13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M13" t="inlineStr" s="2">
@@ -1246,17 +1246,17 @@
     <row r="14" ht="64" customHeight="1">
       <c r="A14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">方案执行</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">工艺能力汇总</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出 PDF</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="2">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="L14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M14" t="inlineStr" s="2">
@@ -1334,17 +1334,17 @@
     <row r="15" ht="64" customHeight="1">
       <c r="A15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">方案执行</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">工艺能力汇总</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出 PDF</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="2">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="L15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M15" t="inlineStr" s="2">
@@ -1421,17 +1421,17 @@
     <row r="16" ht="64" customHeight="1">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">方案执行</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">工艺能力汇总</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出 PDF</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="2">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="L16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M16" t="inlineStr" s="2">
@@ -1508,17 +1508,17 @@
     <row r="17" ht="64" customHeight="1">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">方案执行</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">工艺能力汇总</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出 PDF</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="2">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="L17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M17" t="inlineStr" s="2">

--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/process_capability_summary_pdf_export_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/process_capability_summary_pdf_export_testcases.xlsx
@@ -246,7 +246,7 @@
       </c>
       <c r="L2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M2" t="inlineStr" s="2">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="L15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M15" t="inlineStr" s="2">

--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/process_capability_summary_pdf_export_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/process_capability_summary_pdf_export_testcases.xlsx
@@ -202,7 +202,7 @@
       </c>
       <c r="E2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="2">
@@ -471,7 +471,7 @@
       </c>
       <c r="E5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr" s="2">
@@ -649,7 +649,7 @@
       </c>
       <c r="E7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="2">
@@ -738,7 +738,7 @@
       </c>
       <c r="E8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="2">
@@ -912,7 +912,7 @@
       </c>
       <c r="E10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="2">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="E11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="2">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="2">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="E13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="2">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="E14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="2">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，拥有工艺能力汇总导出权限、审计追踪查看权限和产品 P 的数据权限
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，拥有工艺能力汇总导出权限、审计追踪菜单权限和产品 P 的数据权限
 2. 方案 S 下存在 5 条已分析且已确认的监控项目能力汇总数据
 3. 已成功完成一次方案 S 的 PDF 导出</t>
         </is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="H15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，拥有审计追踪查看权限
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，拥有审计追踪菜单权限
 2. 已存在一条工艺能力汇总导出成功的审计记录</t>
         </is>
       </c>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="H16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，拥有审计追踪查看权限
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，拥有审计追踪菜单权限
 2. 系统已上线工艺能力汇总导出 PDF 功能</t>
         </is>
       </c>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="E17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="2">
